--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56357730</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570092.7130052976</v>
+        <v>570093</v>
       </c>
       <c r="R2" t="n">
-        <v>7011654.064295107</v>
+        <v>7011654</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2015-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103997180</v>
+        <v>103997237</v>
       </c>
       <c r="B3" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570012.999654799</v>
+        <v>570116</v>
       </c>
       <c r="R3" t="n">
-        <v>7011623.017524292</v>
+        <v>7011469</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +859,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +869,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103997183</v>
+        <v>125796772</v>
       </c>
       <c r="B4" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,34 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570116.1518035359</v>
+        <v>570105</v>
       </c>
       <c r="R4" t="n">
-        <v>7011469.208189304</v>
+        <v>7011406</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,75 +986,65 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103997252</v>
+        <v>125796774</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569992.3902180563</v>
+        <v>570069</v>
       </c>
       <c r="R5" t="n">
-        <v>7011594.607861897</v>
+        <v>7011411</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,22 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,40 +1087,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103997237</v>
+        <v>103997180</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1841</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570116.1518035359</v>
+        <v>570013</v>
       </c>
       <c r="R6" t="n">
-        <v>7011469.208189304</v>
+        <v>7011623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103997282</v>
+        <v>103997183</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1841</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1328,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569844.0978332583</v>
+        <v>570116</v>
       </c>
       <c r="R7" t="n">
-        <v>7011643.708702395</v>
+        <v>7011469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,6 +1334,324 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103997252</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stahusbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>569993</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7011595</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125796776</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>569768</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7011642</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125796777</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>569768</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7011642</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357730</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796772</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796774</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997180</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997183</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997252</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796776</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,8 +1699,24 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103997180</v>
+        <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97453</v>
+        <v>97479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,34 +1143,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570013</v>
+        <v>569981</v>
       </c>
       <c r="R6" t="n">
-        <v>7011623</v>
+        <v>7011581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,22 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,39 +1214,45 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997180</t>
+          <t>https://artportalen.se/Sighting/135641244</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103997183</v>
+        <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>97453</v>
+        <v>92016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,34 +1260,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1841</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570116</v>
+        <v>569855</v>
       </c>
       <c r="R7" t="n">
-        <v>7011469</v>
+        <v>7011644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,22 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,74 +1331,80 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997183</t>
+          <t>https://artportalen.se/Sighting/135641233</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103997252</v>
+        <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>92448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569993</v>
+        <v>569851</v>
       </c>
       <c r="R8" t="n">
-        <v>7011595</v>
+        <v>7011647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,22 +1431,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,39 +1448,45 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997252</t>
+          <t>https://artportalen.se/Sighting/135641232</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125796776</v>
+        <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>83307</v>
+        <v>92448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,34 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569768</v>
+        <v>569975</v>
       </c>
       <c r="R9" t="n">
-        <v>7011642</v>
+        <v>7011602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,35 +1564,46 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125796776</t>
+          <t>https://artportalen.se/Sighting/135641241</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125796777</v>
+        <v>103997180</v>
       </c>
       <c r="B10" t="n">
-        <v>58057</v>
+        <v>97453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,34 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Stahusbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569768</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>7011642</v>
+        <v>7011623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,12 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,26 +1691,2198 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997180</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103997183</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stahusbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570116</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7011469</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997183</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135641250</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96454</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>569977</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7011558</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641250</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>103997252</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stahusbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>569993</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7011595</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997252</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135641239</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>569968</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7011581</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641239</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135641236</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>569968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7011593</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641236</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135641240</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>569975</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7011611</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641240</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125796776</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>569768</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7011642</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796776</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135641252</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>569950</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7011561</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641252</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135641234</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>569889</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7011665</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641234</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125796777</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>569768</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7011642</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125796777</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135641231</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>569778</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7011662</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641231</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135641230</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>569770</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7011659</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641230</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135641237</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569976</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7011602</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641237</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135641238</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>569964</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011599</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641238</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135641245</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569991</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7011561</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641245</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135641246</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7011548</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641246</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135641251</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>569959</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7011557</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641251</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135641248</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99048</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>569976</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7011557</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641248</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135641235</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78420</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>569894</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7011636</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641235</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135641243</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92408</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>569975</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7011606</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641243</t>
         </is>
       </c>
     </row>
@@ -1716,6 +3897,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135641236</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>135641240</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>135641252</v>
       </c>
       <c r="B18" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135641235</v>
       </c>
       <c r="B29" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103997180</v>
+        <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97453</v>
+        <v>97511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,34 +1143,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570013</v>
+        <v>569981</v>
       </c>
       <c r="R6" t="n">
-        <v>7011623</v>
+        <v>7011581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,22 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,39 +1214,45 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997180</t>
+          <t>https://artportalen.se/Sighting/135641244</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103997183</v>
+        <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>97453</v>
+        <v>92048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,34 +1260,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1841</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570116</v>
+        <v>569855</v>
       </c>
       <c r="R7" t="n">
-        <v>7011469</v>
+        <v>7011644</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,22 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,74 +1331,80 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997183</t>
+          <t>https://artportalen.se/Sighting/135641233</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103997252</v>
+        <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>92480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stahusbrännan, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569993</v>
+        <v>569851</v>
       </c>
       <c r="R8" t="n">
-        <v>7011595</v>
+        <v>7011647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,22 +1431,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,39 +1448,45 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103997252</t>
+          <t>https://artportalen.se/Sighting/135641232</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125796776</v>
+        <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>83307</v>
+        <v>92480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,34 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569768</v>
+        <v>569975</v>
       </c>
       <c r="R9" t="n">
-        <v>7011642</v>
+        <v>7011602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,12 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,35 +1564,46 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125796776</t>
+          <t>https://artportalen.se/Sighting/135641241</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125796777</v>
+        <v>103997180</v>
       </c>
       <c r="B10" t="n">
-        <v>58057</v>
+        <v>97453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,34 +1611,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Stahusbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569768</v>
+        <v>570013</v>
       </c>
       <c r="R10" t="n">
-        <v>7011642</v>
+        <v>7011623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,12 +1665,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,26 +1691,2198 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997180</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103997183</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stahusbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570116</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7011469</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997183</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135641250</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96486</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>569977</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7011558</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641250</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>103997252</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stahusbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>569993</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7011595</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997252</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135641239</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>569968</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7011581</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641239</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135641236</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>569968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7011593</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641236</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135641240</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>569975</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7011611</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641240</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125796776</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>569768</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7011642</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796776</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135641252</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>569950</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7011561</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641252</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135641234</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>569889</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7011665</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641234</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125796777</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Halbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>569768</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7011642</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125796777</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135641231</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>569778</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7011662</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641231</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135641230</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>569770</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7011659</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641230</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135641237</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>569976</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7011602</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641237</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135641238</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>569964</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011599</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641238</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135641245</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>569991</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7011561</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641245</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135641246</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7011548</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641246</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135641251</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>569959</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7011557</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641251</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135641248</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>569976</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7011557</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641248</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135641235</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>569894</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7011636</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641235</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135641243</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92440</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>569975</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7011606</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641243</t>
         </is>
       </c>
     </row>
@@ -1716,6 +3897,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135641236</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>135641240</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>135641252</v>
       </c>
       <c r="B18" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>135641234</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135641235</v>
       </c>
       <c r="B29" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135641236</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>135641240</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>135641252</v>
       </c>
       <c r="B18" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135641235</v>
       </c>
       <c r="B29" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135641236</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>135641240</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>135641252</v>
       </c>
       <c r="B18" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>135641234</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135641235</v>
       </c>
       <c r="B29" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 43960-2023 artfynd.xlsx
+++ b/artfynd/A 43960-2023 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>135641244</v>
       </c>
       <c r="B6" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135641233</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135641232</v>
       </c>
       <c r="B8" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>135641241</v>
       </c>
       <c r="B9" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135641250</v>
       </c>
       <c r="B12" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>135641239</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>135641236</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>135641240</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>135641252</v>
       </c>
       <c r="B18" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>135641234</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135641231</v>
       </c>
       <c r="B21" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135641230</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135641237</v>
       </c>
       <c r="B23" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135641238</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135641245</v>
       </c>
       <c r="B25" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135641246</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135641251</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135641248</v>
       </c>
       <c r="B28" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135641235</v>
       </c>
       <c r="B29" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>135641243</v>
       </c>
       <c r="B30" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
